--- a/data/trans_orig/POLIPATOLOGIA_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2007</t>
+          <t>Población con dos o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19689</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>49134</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62250</t>
+          <t>61936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474375</t>
+          <t>473711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488085</t>
+          <t>487186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419341</t>
+          <t>418355</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440390</t>
+          <t>440921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>899303</t>
+          <t>899617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924986</t>
+          <t>925469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45189</t>
+          <t>45362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75962</t>
+          <t>74408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112308</t>
+          <t>112493</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103038</t>
+          <t>105393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146314</t>
+          <t>148492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>690300</t>
+          <t>690127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>713162</t>
+          <t>713079</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513186</t>
+          <t>513001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>549532</t>
+          <t>551086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1214668</t>
+          <t>1212490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1257944</t>
+          <t>1255589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47457</t>
+          <t>47357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77479</t>
+          <t>77770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108155</t>
+          <t>109270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149087</t>
+          <t>149558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163886</t>
+          <t>166030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215076</t>
+          <t>217586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561189</t>
+          <t>560898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>591211</t>
+          <t>591311</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540657</t>
+          <t>540186</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581589</t>
+          <t>580474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1113336</t>
+          <t>1110826</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1164526</t>
+          <t>1162382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65553</t>
+          <t>67851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100208</t>
+          <t>101069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130538</t>
+          <t>132418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171419</t>
+          <t>172164</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204489</t>
+          <t>205663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260156</t>
+          <t>262866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>418939</t>
+          <t>418078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>453594</t>
+          <t>451296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344223</t>
+          <t>343478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385104</t>
+          <t>383224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>774633</t>
+          <t>771923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>830300</t>
+          <t>829126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143325</t>
+          <t>143509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181703</t>
+          <t>184095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>189051</t>
+          <t>187712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>227501</t>
+          <t>227642</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344206</t>
+          <t>344844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>400259</t>
+          <t>397049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205007</t>
+          <t>202615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243385</t>
+          <t>243201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176485</t>
+          <t>176344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214935</t>
+          <t>216274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390437</t>
+          <t>393647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>446490</t>
+          <t>445852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>136803</t>
+          <t>137935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170510</t>
+          <t>169904</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>231522</t>
+          <t>231168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>262486</t>
+          <t>263192</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>378152</t>
+          <t>377715</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>423815</t>
+          <t>423207</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>122073</t>
+          <t>122679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155780</t>
+          <t>154648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80448</t>
+          <t>79742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111412</t>
+          <t>111766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>211702</t>
+          <t>212310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>257365</t>
+          <t>257802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131463</t>
+          <t>131141</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157536</t>
+          <t>158420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252925</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283153</t>
+          <t>282830</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394643</t>
+          <t>393103</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434219</t>
+          <t>431699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52347</t>
+          <t>51463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78420</t>
+          <t>78742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>51078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80983</t>
+          <t>81165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>109572</t>
+          <t>112092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>149148</t>
+          <t>150688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>602418</t>
+          <t>604686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>688582</t>
+          <t>692536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1079246</t>
+          <t>1079368</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1194125</t>
+          <t>1189882</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1699278</t>
+          <t>1710286</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1855089</t>
+          <t>1847148</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2587961</t>
+          <t>2584007</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2674125</t>
+          <t>2671857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2185072</t>
+          <t>2189315</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2299951</t>
+          <t>2299829</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4800652</t>
+          <t>4808593</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4956463</t>
+          <t>4945455</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2012</t>
+          <t>Población con dos o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>31333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>56695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41232</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>72191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432296</t>
+          <t>432676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446684</t>
+          <t>446510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>373207</t>
+          <t>373535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>398384</t>
+          <t>398897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>814237</t>
+          <t>812185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>843144</t>
+          <t>841299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62901</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>55470</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88224</t>
+          <t>88009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99190</t>
+          <t>98604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140017</t>
+          <t>140941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>624186</t>
+          <t>624549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>651500</t>
+          <t>652151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>522031</t>
+          <t>522246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555290</t>
+          <t>554785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1157325</t>
+          <t>1156401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1198152</t>
+          <t>1198738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53827</t>
+          <t>52408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86049</t>
+          <t>85644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144223</t>
+          <t>142820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190614</t>
+          <t>190629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206678</t>
+          <t>205424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>265714</t>
+          <t>264417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>595814</t>
+          <t>596219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628036</t>
+          <t>629455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520236</t>
+          <t>520221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>566627</t>
+          <t>568030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1126998</t>
+          <t>1128295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1186034</t>
+          <t>1187288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83454</t>
+          <t>81789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122902</t>
+          <t>121228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178348</t>
+          <t>181843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227345</t>
+          <t>230477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>270890</t>
+          <t>273553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>335219</t>
+          <t>341964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>491715</t>
+          <t>493389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>531163</t>
+          <t>532828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>388854</t>
+          <t>385722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>437851</t>
+          <t>434356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>895597</t>
+          <t>888852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>959926</t>
+          <t>957263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152720</t>
+          <t>152807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194913</t>
+          <t>195813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251097</t>
+          <t>249674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294028</t>
+          <t>293918</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>413883</t>
+          <t>416788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>477967</t>
+          <t>479295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>234516</t>
+          <t>233616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>276709</t>
+          <t>276622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153772</t>
+          <t>153882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196703</t>
+          <t>198126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>399262</t>
+          <t>397934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>463346</t>
+          <t>460441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>202864</t>
+          <t>205111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237018</t>
+          <t>238216</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254540</t>
+          <t>254156</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>286270</t>
+          <t>286534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>468242</t>
+          <t>471248</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>515783</t>
+          <t>517638</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72768</t>
+          <t>71570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106922</t>
+          <t>104675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>67462</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99456</t>
+          <t>99840</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>147999</t>
+          <t>146144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>195540</t>
+          <t>192534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191374</t>
+          <t>191677</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>216862</t>
+          <t>217926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>335688</t>
+          <t>336934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>360829</t>
+          <t>361610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>535948</t>
+          <t>536491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>572659</t>
+          <t>570546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32989</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58477</t>
+          <t>58174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53291</t>
+          <t>52045</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66171</t>
+          <t>68284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102882</t>
+          <t>102339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>787129</t>
+          <t>782057</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>888717</t>
+          <t>883353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1320215</t>
+          <t>1319650</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1442583</t>
+          <t>1442411</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2130636</t>
+          <t>2129607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2286226</t>
+          <t>2282063</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2538062</t>
+          <t>2543426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2639650</t>
+          <t>2644722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2115726</t>
+          <t>2115898</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2238094</t>
+          <t>2238659</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4698862</t>
+          <t>4703025</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4854452</t>
+          <t>4855481</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2016</t>
+          <t>Población con dos o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28836</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52000</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40643</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68406</t>
+          <t>69082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395632</t>
+          <t>395863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410652</t>
+          <t>410849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>343755</t>
+          <t>344810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>366919</t>
+          <t>367927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>746812</t>
+          <t>746136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774575</t>
+          <t>774168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>49180</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53845</t>
+          <t>53974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84398</t>
+          <t>84759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86380</t>
+          <t>86148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124366</t>
+          <t>123767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>540464</t>
+          <t>541316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>565385</t>
+          <t>566544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479146</t>
+          <t>478785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509699</t>
+          <t>509570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1029674</t>
+          <t>1030273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1067660</t>
+          <t>1067892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47170</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78713</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91530</t>
+          <t>90951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127427</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144312</t>
+          <t>148145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194363</t>
+          <t>196004</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590384</t>
+          <t>590098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621927</t>
+          <t>620994</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533959</t>
+          <t>532154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>569856</t>
+          <t>570435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1136120</t>
+          <t>1134479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1186171</t>
+          <t>1182338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120508</t>
+          <t>119204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163874</t>
+          <t>163415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181246</t>
+          <t>181279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>231886</t>
+          <t>228864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>316125</t>
+          <t>313583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381451</t>
+          <t>380157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>482174</t>
+          <t>482633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>525540</t>
+          <t>526844</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>417191</t>
+          <t>420213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>467831</t>
+          <t>467798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>913674</t>
+          <t>914968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>979000</t>
+          <t>981542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155316</t>
+          <t>155368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>200365</t>
+          <t>198492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>246914</t>
+          <t>246064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>295020</t>
+          <t>293368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>412249</t>
+          <t>413748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>481478</t>
+          <t>479502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>277553</t>
+          <t>279426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322602</t>
+          <t>322550</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201829</t>
+          <t>203481</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>249935</t>
+          <t>250785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>493289</t>
+          <t>495265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>562518</t>
+          <t>561019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>171318</t>
+          <t>173496</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>208864</t>
+          <t>207781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>246964</t>
+          <t>245085</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>283396</t>
+          <t>282038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>428160</t>
+          <t>425012</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>479023</t>
+          <t>476531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125466</t>
+          <t>126549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163012</t>
+          <t>160834</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94366</t>
+          <t>95724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>130798</t>
+          <t>132677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>233069</t>
+          <t>235561</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>283932</t>
+          <t>287080</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>174576</t>
+          <t>177183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201091</t>
+          <t>201941</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>304647</t>
+          <t>305650</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>340969</t>
+          <t>341011</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>489709</t>
+          <t>491868</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>536404</t>
+          <t>535563</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>55057</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82422</t>
+          <t>79815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59200</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95522</t>
+          <t>94519</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120763</t>
+          <t>121604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>167458</t>
+          <t>165299</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>764151</t>
+          <t>759917</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>859191</t>
+          <t>856995</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1220979</t>
+          <t>1225763</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1338743</t>
+          <t>1344973</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2007492</t>
+          <t>2004080</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2164548</t>
+          <t>2159177</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2535159</t>
+          <t>2537355</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2630199</t>
+          <t>2634433</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2205799</t>
+          <t>2199569</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2323563</t>
+          <t>2318779</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4774344</t>
+          <t>4779715</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4931400</t>
+          <t>4934812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,12%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2023</t>
+          <t>Población con dos o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t>26250</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72021</t>
+          <t>75026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42956</t>
+          <t>44452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82794</t>
+          <t>80192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81031</t>
+          <t>78997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140124</t>
+          <t>137298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327966</t>
+          <t>324961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373447</t>
+          <t>373737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230406</t>
+          <t>233008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270244</t>
+          <t>268748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573063</t>
+          <t>575889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>632156</t>
+          <t>634190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33422</t>
+          <t>33953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64902</t>
+          <t>63155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109366</t>
+          <t>110832</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300670</t>
+          <t>302279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151537</t>
+          <t>154540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>393685</t>
+          <t>394511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358645</t>
+          <t>360392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>390125</t>
+          <t>389594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211423</t>
+          <t>209814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>402727</t>
+          <t>401261</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>541955</t>
+          <t>541129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>784103</t>
+          <t>781100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,48%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63858</t>
+          <t>61924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97280</t>
+          <t>95159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116081</t>
+          <t>112391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174184</t>
+          <t>171815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191481</t>
+          <t>194783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>255737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>439058</t>
+          <t>441179</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472480</t>
+          <t>474414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>417818</t>
+          <t>420187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>475921</t>
+          <t>479611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871557</t>
+          <t>872603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936859</t>
+          <t>933557</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87630</t>
+          <t>88765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280567</t>
+          <t>282995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>249847</t>
+          <t>245844</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>320786</t>
+          <t>319780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>270835</t>
+          <t>311450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>593493</t>
+          <t>598169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607219</t>
+          <t>604791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>800156</t>
+          <t>799021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>392095</t>
+          <t>393101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463034</t>
+          <t>467037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1007174</t>
+          <t>1002498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1329832</t>
+          <t>1289217</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>242248</t>
+          <t>241576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287442</t>
+          <t>287178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>288131</t>
+          <t>287457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>324198</t>
+          <t>323613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>538342</t>
+          <t>543906</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>597469</t>
+          <t>600414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>273792</t>
+          <t>274056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>318986</t>
+          <t>319658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223707</t>
+          <t>224292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>259774</t>
+          <t>260448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>511670</t>
+          <t>508725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570797</t>
+          <t>565233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>196176</t>
+          <t>196405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>225004</t>
+          <t>224825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>427535</t>
+          <t>425764</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>560085</t>
+          <t>555481</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>622963</t>
+          <t>623732</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>825125</t>
+          <t>830259</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143161</t>
+          <t>143340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171989</t>
+          <t>171760</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48283</t>
+          <t>52887</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>180833</t>
+          <t>182604</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151408</t>
+          <t>146274</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353570</t>
+          <t>352801</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199839</t>
+          <t>197941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222888</t>
+          <t>222490</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343390</t>
+          <t>343151</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>366168</t>
+          <t>364719</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>548962</t>
+          <t>548034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>582076</t>
+          <t>580821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59871</t>
+          <t>60269</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82920</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59663</t>
+          <t>61112</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82441</t>
+          <t>82680</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>126514</t>
+          <t>127769</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>159628</t>
+          <t>160556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>835717</t>
+          <t>805141</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1156801</t>
+          <t>1153971</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1683891</t>
+          <t>1684866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2167780</t>
+          <t>2187398</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2608595</t>
+          <t>2625165</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3302182</t>
+          <t>3271032</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2303016</t>
+          <t>2305846</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2624100</t>
+          <t>2654676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1544500</t>
+          <t>1524882</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2028389</t>
+          <t>2027414</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3869915</t>
+          <t>3901065</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4563502</t>
+          <t>4546932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49134</t>
+          <t>48751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>36227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61936</t>
+          <t>62593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473711</t>
+          <t>473775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487186</t>
+          <t>488054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>418355</t>
+          <t>418738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440921</t>
+          <t>440924</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>899617</t>
+          <t>898960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>925469</t>
+          <t>925326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>44456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74408</t>
+          <t>76442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112493</t>
+          <t>112348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105393</t>
+          <t>106363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148492</t>
+          <t>150614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>690127</t>
+          <t>691033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>713079</t>
+          <t>712152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513001</t>
+          <t>513146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>551086</t>
+          <t>549052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1212490</t>
+          <t>1210368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1255589</t>
+          <t>1254619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47357</t>
+          <t>48022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>76529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109270</t>
+          <t>107764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149558</t>
+          <t>150839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166030</t>
+          <t>163795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217586</t>
+          <t>216484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>560898</t>
+          <t>562139</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>591311</t>
+          <t>590646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540186</t>
+          <t>538905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>580474</t>
+          <t>581980</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1110826</t>
+          <t>1111928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1162382</t>
+          <t>1164617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67851</t>
+          <t>64926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101069</t>
+          <t>99967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132418</t>
+          <t>128676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172164</t>
+          <t>171955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205663</t>
+          <t>205957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262866</t>
+          <t>258972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>418078</t>
+          <t>419180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>451296</t>
+          <t>454221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343478</t>
+          <t>343687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383224</t>
+          <t>386966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>771923</t>
+          <t>775817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>829126</t>
+          <t>828832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143509</t>
+          <t>144022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>184095</t>
+          <t>182598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187712</t>
+          <t>186905</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>227642</t>
+          <t>226983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344844</t>
+          <t>342763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>397049</t>
+          <t>399071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202615</t>
+          <t>204112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243201</t>
+          <t>242688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176344</t>
+          <t>177003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216274</t>
+          <t>217081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393647</t>
+          <t>391625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>445852</t>
+          <t>447933</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>137935</t>
+          <t>137471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169904</t>
+          <t>169908</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>231168</t>
+          <t>232930</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>263192</t>
+          <t>263413</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>377715</t>
+          <t>376808</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>423207</t>
+          <t>423294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>122679</t>
+          <t>122675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154648</t>
+          <t>155112</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>79521</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111766</t>
+          <t>110004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>212310</t>
+          <t>212223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>257802</t>
+          <t>258709</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131141</t>
+          <t>131758</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158420</t>
+          <t>158112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252743</t>
+          <t>253859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>282830</t>
+          <t>282804</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>393103</t>
+          <t>393894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431699</t>
+          <t>433521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51463</t>
+          <t>51771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78742</t>
+          <t>78125</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51078</t>
+          <t>51104</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81165</t>
+          <t>80049</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112092</t>
+          <t>110270</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>150688</t>
+          <t>149897</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>604686</t>
+          <t>602391</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>692536</t>
+          <t>693201</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1079368</t>
+          <t>1078673</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1189882</t>
+          <t>1189146</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1710286</t>
+          <t>1711947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1847148</t>
+          <t>1860969</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2584007</t>
+          <t>2583342</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2671857</t>
+          <t>2674152</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2189315</t>
+          <t>2190051</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2299829</t>
+          <t>2300524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4808593</t>
+          <t>4794772</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4945455</t>
+          <t>4943794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>21230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31333</t>
+          <t>31443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56695</t>
+          <t>55517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43077</t>
+          <t>42627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72191</t>
+          <t>69724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432676</t>
+          <t>432916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446510</t>
+          <t>446534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>373535</t>
+          <t>374713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>398897</t>
+          <t>398787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>812185</t>
+          <t>814652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>841299</t>
+          <t>841749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>35378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62538</t>
+          <t>63446</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,82 +4070,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>69950</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>54537</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>85919</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>118075</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>101531</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>140594</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>9,1%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>69950</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>55470</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>88009</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>118075</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>98604</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>140941</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>624549</t>
+          <t>623641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>652151</t>
+          <t>651709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,82 +4183,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>90,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>540305</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>524336</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>555718</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1179267</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1156748</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1195811</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>90,9%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>540305</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>522246</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>554785</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1179267</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1156401</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1198738</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52408</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85644</t>
+          <t>85859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142820</t>
+          <t>143715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190629</t>
+          <t>190305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205424</t>
+          <t>206007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264417</t>
+          <t>263960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596219</t>
+          <t>596004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629455</t>
+          <t>629353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520221</t>
+          <t>520545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>568030</t>
+          <t>567135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1128295</t>
+          <t>1128752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1187288</t>
+          <t>1186705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81789</t>
+          <t>83138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121228</t>
+          <t>121915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181843</t>
+          <t>180798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>230477</t>
+          <t>231233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273553</t>
+          <t>272708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>341964</t>
+          <t>336546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493389</t>
+          <t>492702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>532828</t>
+          <t>531479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385722</t>
+          <t>384966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>434356</t>
+          <t>435401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>888852</t>
+          <t>894270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>957263</t>
+          <t>958108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152807</t>
+          <t>153027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195813</t>
+          <t>196291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>249674</t>
+          <t>251091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>293918</t>
+          <t>296978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>416788</t>
+          <t>417822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>479295</t>
+          <t>477073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233616</t>
+          <t>233138</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>276622</t>
+          <t>276402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153882</t>
+          <t>150822</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198126</t>
+          <t>196709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397934</t>
+          <t>400156</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>460441</t>
+          <t>459407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205111</t>
+          <t>205703</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238216</t>
+          <t>238874</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254156</t>
+          <t>254109</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>286534</t>
+          <t>287602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>471248</t>
+          <t>470092</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>517638</t>
+          <t>516233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71570</t>
+          <t>70912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104675</t>
+          <t>104083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67462</t>
+          <t>66394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99840</t>
+          <t>99887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>146144</t>
+          <t>147549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>192534</t>
+          <t>193690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191677</t>
+          <t>189692</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>217926</t>
+          <t>215669</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>336934</t>
+          <t>337292</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>361610</t>
+          <t>361691</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>536491</t>
+          <t>536162</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>570546</t>
+          <t>572750</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58174</t>
+          <t>60159</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>51687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>68284</t>
+          <t>66080</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102339</t>
+          <t>102668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>782057</t>
+          <t>780825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>883353</t>
+          <t>885096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1319650</t>
+          <t>1321643</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1442411</t>
+          <t>1434835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2129607</t>
+          <t>2132730</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2282063</t>
+          <t>2295311</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2543426</t>
+          <t>2541683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2644722</t>
+          <t>2645954</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2115898</t>
+          <t>2123474</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2238659</t>
+          <t>2236666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4703025</t>
+          <t>4689777</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4855481</t>
+          <t>4852358</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>28236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69082</t>
+          <t>69918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395863</t>
+          <t>394810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410849</t>
+          <t>410711</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>344810</t>
+          <t>346298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>367927</t>
+          <t>367519</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>746136</t>
+          <t>745300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774168</t>
+          <t>773501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49180</t>
+          <t>50363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53974</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>84247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86148</t>
+          <t>86566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123767</t>
+          <t>124987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>541316</t>
+          <t>540133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>566544</t>
+          <t>565529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>478785</t>
+          <t>479297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509570</t>
+          <t>509678</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1030273</t>
+          <t>1029053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1067892</t>
+          <t>1067474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>48589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78999</t>
+          <t>78390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90951</t>
+          <t>90415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>128604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148145</t>
+          <t>147103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196004</t>
+          <t>196630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590098</t>
+          <t>590707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620994</t>
+          <t>620508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532154</t>
+          <t>532782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>570435</t>
+          <t>570971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1134479</t>
+          <t>1133853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1182338</t>
+          <t>1183380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119204</t>
+          <t>119920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163415</t>
+          <t>165984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181279</t>
+          <t>183723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228864</t>
+          <t>232302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>313583</t>
+          <t>314352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>380157</t>
+          <t>381646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>482633</t>
+          <t>480064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>526844</t>
+          <t>526128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>420213</t>
+          <t>416775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>467798</t>
+          <t>465354</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>914968</t>
+          <t>913479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>981542</t>
+          <t>980773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155368</t>
+          <t>155552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198492</t>
+          <t>200499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>246064</t>
+          <t>248454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>293368</t>
+          <t>293356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>413748</t>
+          <t>412100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>479502</t>
+          <t>479510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>279426</t>
+          <t>277419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322550</t>
+          <t>322366</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203481</t>
+          <t>203493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250785</t>
+          <t>248395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>495265</t>
+          <t>495257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>561019</t>
+          <t>562667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>173496</t>
+          <t>172715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>207781</t>
+          <t>208422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>245085</t>
+          <t>243567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282038</t>
+          <t>281205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>425012</t>
+          <t>428980</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>476531</t>
+          <t>481441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126549</t>
+          <t>125908</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160834</t>
+          <t>161615</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>95724</t>
+          <t>96557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132677</t>
+          <t>134195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235561</t>
+          <t>230651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>287080</t>
+          <t>283112</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177183</t>
+          <t>177274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201941</t>
+          <t>202915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>305650</t>
+          <t>303174</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>341011</t>
+          <t>341255</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>491868</t>
+          <t>489888</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>535563</t>
+          <t>535063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55057</t>
+          <t>54083</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>79815</t>
+          <t>79724</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59158</t>
+          <t>58914</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>94519</t>
+          <t>96995</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>121604</t>
+          <t>122104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>165299</t>
+          <t>167279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>759917</t>
+          <t>759512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>856995</t>
+          <t>861636</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1225763</t>
+          <t>1218532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1344973</t>
+          <t>1342725</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2004080</t>
+          <t>2009158</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2159177</t>
+          <t>2167617</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2537355</t>
+          <t>2532714</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2634433</t>
+          <t>2634838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2199569</t>
+          <t>2201817</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2318779</t>
+          <t>2326010</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4779715</t>
+          <t>4771275</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4934812</t>
+          <t>4929734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46589</t>
+          <t>44285</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>26180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75026</t>
+          <t>67875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>74034</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>53740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80192</t>
+          <t>99922</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>107728</t>
+          <t>118319</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78997</t>
+          <t>89407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137298</t>
+          <t>149509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>353398</t>
+          <t>363508</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>324961</t>
+          <t>339918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373737</t>
+          <t>381613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>252061</t>
+          <t>288478</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233008</t>
+          <t>262590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268748</t>
+          <t>308772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>605459</t>
+          <t>651986</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575889</t>
+          <t>620796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>634190</t>
+          <t>680898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47712</t>
+          <t>55010</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33953</t>
+          <t>40489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63155</t>
+          <t>73395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>170213</t>
+          <t>109451</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110832</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302279</t>
+          <t>127950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>217925</t>
+          <t>164461</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154540</t>
+          <t>139863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>394511</t>
+          <t>191888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>375835</t>
+          <t>421880</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360392</t>
+          <t>403495</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389594</t>
+          <t>436401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>341880</t>
+          <t>392282</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209814</t>
+          <t>373783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>401261</t>
+          <t>412043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>717715</t>
+          <t>814162</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>541129</t>
+          <t>786735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>781100</t>
+          <t>838760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>86474</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61924</t>
+          <t>68234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95159</t>
+          <t>105364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>150508</t>
+          <t>176798</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112391</t>
+          <t>156428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171815</t>
+          <t>196114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>229389</t>
+          <t>263271</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194783</t>
+          <t>238760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255737</t>
+          <t>292024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>457457</t>
+          <t>534363</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>441179</t>
+          <t>515473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474414</t>
+          <t>552603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>441494</t>
+          <t>446395</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>420187</t>
+          <t>427079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>479611</t>
+          <t>466765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>898951</t>
+          <t>980758</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>872603</t>
+          <t>952005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933557</t>
+          <t>1005269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>80,81%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>196233</t>
+          <t>211691</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88765</t>
+          <t>188302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282995</t>
+          <t>239390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>296087</t>
+          <t>317964</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>245844</t>
+          <t>294818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>319780</t>
+          <t>337432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>492320</t>
+          <t>529655</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>311450</t>
+          <t>496234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>598169</t>
+          <t>561082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>691553</t>
+          <t>488926</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604791</t>
+          <t>461227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>799021</t>
+          <t>512315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>416794</t>
+          <t>418922</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393101</t>
+          <t>399454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>467037</t>
+          <t>442068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1108347</t>
+          <t>907849</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1002498</t>
+          <t>876422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1289217</t>
+          <t>941270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>263495</t>
+          <t>280280</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>241576</t>
+          <t>258611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287178</t>
+          <t>304907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>306422</t>
+          <t>343542</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287457</t>
+          <t>324719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>323613</t>
+          <t>361660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>569917</t>
+          <t>623822</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>543906</t>
+          <t>595106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>600414</t>
+          <t>655131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>297739</t>
+          <t>329066</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274056</t>
+          <t>304439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319658</t>
+          <t>350735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>241483</t>
+          <t>265313</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224292</t>
+          <t>247195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260448</t>
+          <t>284136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>539222</t>
+          <t>594380</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>508725</t>
+          <t>563071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>565233</t>
+          <t>623096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,15%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>210878</t>
+          <t>231964</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>196405</t>
+          <t>214620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>224825</t>
+          <t>248459</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>492429</t>
+          <t>315581</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>425764</t>
+          <t>303258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>555481</t>
+          <t>331076</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>703307</t>
+          <t>547545</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>623732</t>
+          <t>526485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>830259</t>
+          <t>569554</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>157287</t>
+          <t>175116</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>158621</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171760</t>
+          <t>192460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>115939</t>
+          <t>123585</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52887</t>
+          <t>108090</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182604</t>
+          <t>135908</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>273226</t>
+          <t>298701</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>146274</t>
+          <t>276692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352801</t>
+          <t>319761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>210891</t>
+          <t>231116</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197941</t>
+          <t>217114</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222490</t>
+          <t>244149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>355172</t>
+          <t>386772</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343151</t>
+          <t>373572</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>364719</t>
+          <t>397751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>566063</t>
+          <t>617888</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>548034</t>
+          <t>600674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>580821</t>
+          <t>637318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>71868</t>
+          <t>79082</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60269</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84818</t>
+          <t>93084</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>70659</t>
+          <t>77837</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61112</t>
+          <t>66858</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82680</t>
+          <t>91037</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>142527</t>
+          <t>156919</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127769</t>
+          <t>137489</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>160556</t>
+          <t>174133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1054679</t>
+          <t>1140819</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>805141</t>
+          <t>1085220</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1153971</t>
+          <t>1205055</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1831969</t>
+          <t>1724142</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1684866</t>
+          <t>1673647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2187398</t>
+          <t>1779174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2886648</t>
+          <t>2864962</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2625165</t>
+          <t>2775215</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3271032</t>
+          <t>2946273</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2405138</t>
+          <t>2391943</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2305846</t>
+          <t>2327707</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2654676</t>
+          <t>2447542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1880311</t>
+          <t>2012812</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1524882</t>
+          <t>1957780</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2027414</t>
+          <t>2063307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4285449</t>
+          <t>4404754</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3901065</t>
+          <t>4323443</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4546932</t>
+          <t>4494501</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
